--- a/business1-1.xlsx
+++ b/business1-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seigo\Desktop\授業\2025後期授業\ビジネス実践演習\11月５日\R練習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B9706D-B564-408A-B165-F277F7F94CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9989F66-9C48-4A59-ADE2-5F7654E6A54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="事例1" sheetId="1" r:id="rId1"/>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="3" max="3" width="12.625" customWidth="1"/>
@@ -418,72 +418,142 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2">
-        <v>920</v>
+        <v>58543</v>
       </c>
       <c r="B2" s="2">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="C2" s="2">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="D2" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2">
-        <v>850</v>
+        <v>61455</v>
       </c>
       <c r="B3" s="2">
-        <v>90</v>
+        <v>650</v>
       </c>
       <c r="C3" s="2">
-        <v>280</v>
+        <v>800</v>
       </c>
       <c r="D3" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2">
-        <v>990</v>
+        <v>68014</v>
       </c>
       <c r="B4" s="2">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="C4" s="2">
-        <v>350</v>
+        <v>880</v>
       </c>
       <c r="D4" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2">
-        <v>760</v>
+        <v>70215</v>
       </c>
       <c r="B5" s="2">
-        <v>70</v>
+        <v>750</v>
       </c>
       <c r="C5" s="2">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="D5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
-        <v>890</v>
+        <v>77391</v>
       </c>
       <c r="B6" s="2">
-        <v>95</v>
+        <v>800</v>
       </c>
       <c r="C6" s="2">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>80772</v>
+      </c>
+      <c r="B7">
+        <v>850</v>
+      </c>
+      <c r="C7">
+        <v>1050</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>87520</v>
+      </c>
+      <c r="B8">
+        <v>900</v>
+      </c>
+      <c r="C8">
+        <v>1150</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>91075</v>
+      </c>
+      <c r="B9">
+        <v>950</v>
+      </c>
+      <c r="C9">
+        <v>1200</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>97880</v>
+      </c>
+      <c r="B10">
+        <v>1000</v>
+      </c>
+      <c r="C10">
+        <v>1300</v>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>106942</v>
+      </c>
+      <c r="B11">
+        <v>1100</v>
+      </c>
+      <c r="C11">
+        <v>1400</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
